--- a/reference/origins/product info/WA_Edibles_By_Brand_Sectioned.xlsx
+++ b/reference/origins/product info/WA_Edibles_By_Brand_Sectioned.xlsx
@@ -758,7 +758,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Constellation Cannabis</t>
+          <t>Constellation</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Constellation Cannabis</t>
+          <t>Constellation</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,7 +884,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Constellation Cannabis</t>
+          <t>Constellation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Constellation Cannabis</t>
+          <t>Constellation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Constellation Cannabis</t>
+          <t>Constellation</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Constellation Cannabis</t>
+          <t>Constellation</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
